--- a/nr-update-med-administration-descr/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
+++ b/nr-update-med-administration-descr/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-09T09:28:23+00:00</t>
+    <t>2024-09-09T09:28:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
